--- a/quizzes/005_dimensionality_reduction_quiz--quizzes.xlsx
+++ b/quizzes/005_dimensionality_reduction_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is Dimensionality Reduction?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This quiz will cover various aspects of dimensionality reduction.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>question 1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Question 1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A way to simplify complex data by reducing its dimensionality.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1_answer_1</t>
+          <t>question_2_answer_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>answer 1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>A way to simplify complex data by reducing its dimensionality.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>It helps in reducing the curse of dimensionality.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_1_answer_2</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>answer 2</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is the main idea behind Dimensionality Reduction?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>It is used to remove the noise from the data.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>question_4_answer_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>question 2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Reducing the number of features to improve model performance.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>By removing irrelevant features, we can improve the accuracy of our model.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_2_answer_1</t>
+          <t>question_4_answer_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>answer 1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Reducing the number of features to improve model interpretability.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>It makes it easier to understand the model and its results.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -658,15 +682,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_2_answer_2</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>answer 2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>When is Dimensionality Reduction used?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>It is used in various fields such as data analysis and machine learning.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -681,15 +709,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question_5_answer_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>question 3</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Dimensionality reduction is used in data analysis to reduce the dimensionality of high-dimensional data.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>It helps in reducing the computational complexity of the model.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,15 +736,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_3_answer_1</t>
+          <t>question_5_answer_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>answer 1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Reducing the dimensionality of data to improve model interpretability.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>It makes it easier to understand the relationships between variables.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -727,15 +763,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_3_answer_2</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>answer 2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What are the benefits of Dimensionality Reduction?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>It can improve model performance.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_6_answer_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>question 4</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Dimensionality reduction can improve model performance.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>It can reduce the overfitting of the model.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_4_answer_1</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>answer 1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What are the challenges of Dimensionality Reduction?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>It can be challenging to choose the right dimensionality reduction technique.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_4_answer_2</t>
+          <t>question_7_answer_1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>answer 2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Dimensionality reduction can be challenging to choose the right technique.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>It depends on the type of data and the problem.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -819,15 +871,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_7_answer_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>question 5</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Choosing the right technique depends on the type of data.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>It requires a deep understanding of the data and the problem.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>no</t>
@@ -842,15 +898,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_5_answer_1</t>
+          <t>question_7_answer_2_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>answer 1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Choosing the right technique requires a deep understanding of the problem.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>It also requires the ability to measure the performance of the model.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
@@ -865,15 +925,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question_5_answer_2</t>
+          <t>question_7_answer_1_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>answer 2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Choosing the right technique requires the ability to measure the performance of the model.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>It helps in avoiding overfitting.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -888,15 +952,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>question 6</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>What are some real-world applications of Dimensionality Reduction?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>It is used in image and speech recognition.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>no</t>
@@ -911,15 +979,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>question_6_answer_1</t>
+          <t>question_8_answer_1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>answer 1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Dimensionality reduction is used in image recognition.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>It can improve the performance of the model.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
@@ -934,15 +1006,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>question_6_answer_2</t>
+          <t>question_8_answer_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>answer 2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Reducing the dimensionality of images to improve model performance.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>It can reduce the amount of data needed for training.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>no</t>
@@ -957,15 +1033,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>question_8_answer_2_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>question 7</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Reducing the dimensionality of images to reduce the amount of data needed for training.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>It can help in real-time applications.</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
@@ -986,9 +1066,9 @@
   <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1016,12 +1096,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>dimensionality_reduction_is_a_process_of_reducing_the_number_of_variables_or_features_in_a_dataset.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dimensionality reduction is a process of reducing the number of variables or features in a dataset.</t>
         </is>
       </c>
     </row>
@@ -1033,624 +1113,624 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dimensionality_reduction_is_a_machine_learning_technique_used_for_data_preprocessing.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dimensionality reduction is a machine learning technique used for data preprocessing.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_1_answer_1_choices</t>
+          <t>question_2_answer_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>reducing_the_number_of_variables_or_features_in_a_dataset.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Reducing the number of variables or features in a dataset.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_1_answer_1_choices</t>
+          <t>question_2_answer_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>reducing_the_amount_of_data_to_make_it_more_efficient.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reducing the amount of data to make it more efficient.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_1_answer_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>reducing_the_number_of_features_to_improve_model_performance.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Reducing the number of features to improve model performance.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_1_answer_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>reducing_the_number_of_variables_to_make_the_model_simpler.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reducing the number of variables to make the model simpler.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_4_answer_1_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>reducing_the_feature_space_to_avoid_overfitting.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Reducing the feature space to avoid overfitting.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_4_answer_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>reducing_the_number_of_features_to_improve_model_interpretability.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reducing the number of features to improve model interpretability.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_2_answer_1_choices</t>
+          <t>question_4_answer_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>reducing_the_dimensionality_of_high-dimensional_data.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Reducing the dimensionality of high-dimensional data.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_2_answer_1_choices</t>
+          <t>question_4_answer_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>reducing_the_number_of_features_to_reduce_the_model_complexity.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reducing the number of features to reduce the model complexity.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_2_answer_2_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>dimensionality_reduction_is_used_in_data_analysis_to_reduce_the_dimensionality_of_high-dimensional_data.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dimensionality reduction is used in data analysis to reduce the dimensionality of high-dimensional data.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_2_answer_2_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dimensionality_reduction_is_used_in_machine_learning_to_improve_model_performance.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dimensionality reduction is used in machine learning to improve model performance.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_5_answer_1_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>reducing_the_number_of_features_to_improve_data_visualization.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Reducing the number of features to improve data visualization.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_5_answer_1_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>reducing_the_dimensionality_of_data_to_improve_model_interpretability.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reducing the dimensionality of data to improve model interpretability.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_3_answer_1_choices</t>
+          <t>question_5_answer_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>reducing_the_number_of_variables_to_improve_model_simplicity.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Reducing the number of variables to improve model simplicity.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_3_answer_1_choices</t>
+          <t>question_5_answer_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>reducing_the_dimensionality_of_data_to_reduce_the_model_complexity.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reducing the dimensionality of data to reduce the model complexity.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_3_answer_2_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>dimensionality_reduction_can_improve_model_performance.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dimensionality reduction can improve model performance.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>question_3_answer_2_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dimensionality_reduction_can_reduce_the_model_complexity.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dimensionality reduction can reduce the model complexity.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_6_answer_1_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>reducing_the_number_of_features_to_improve_model_accuracy.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Reducing the number of features to improve model accuracy.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_6_answer_1_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>reducing_the_dimensionality_of_data_to_improve_model_interpretability.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reducing the dimensionality of data to improve model interpretability.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>question_4_answer_1_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>dimensionality_reduction_can_be_challenging_to_choose_the_right_technique.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dimensionality reduction can be challenging to choose the right technique.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>question_4_answer_1_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dimensionality_reduction_can_be_challenging_to_balance_between_overfitting_and_underfitting.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dimensionality reduction can be challenging to balance between overfitting and underfitting.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>question_4_answer_2_choices</t>
+          <t>question_7_answer_1_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>choosing_the_right_technique_depends_on_the_type_of_data.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Choosing the right technique depends on the type of data.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>question_4_answer_2_choices</t>
+          <t>question_7_answer_1_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>choosing_the_right_technique_depends_on_the_problem.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Choosing the right technique depends on the problem.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_7_answer_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>choosing_the_right_technique_requires_a_deep_understanding_of_the_data.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Choosing the right technique requires a deep understanding of the data.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>question_7_answer_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>choosing_the_right_technique_requires_a_deep_understanding_of_the_problem.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Choosing the right technique requires a deep understanding of the problem.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>question_5_answer_1_choices</t>
+          <t>question_7_answer_2_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>choosing_the_right_technique_requires_the_ability_to_measure_the_performance_of_the_model.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Choosing the right technique requires the ability to measure the performance of the model.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>question_5_answer_1_choices</t>
+          <t>question_7_answer_2_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>choosing_the_right_technique_requires_the_ability_to_interpret_the_results.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Choosing the right technique requires the ability to interpret the results.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>question_5_answer_2_choices</t>
+          <t>question_7_answer_1_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>avoiding_overfitting_by_reducing_the_number_of_features.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Avoiding overfitting by reducing the number of features.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>question_5_answer_2_choices</t>
+          <t>question_7_answer_1_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>avoiding_overfitting_by_reducing_the_dimensionality_of_data.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Avoiding overfitting by reducing the dimensionality of data.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>dimensionality_reduction_is_used_in_image_recognition.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Dimensionality reduction is used in image recognition.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>dimensionality_reduction_is_used_in_speech_recognition.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Dimensionality reduction is used in speech recognition.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>question_6_answer_1_choices</t>
+          <t>question_8_answer_1_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>reducing_the_dimensionality_of_images_to_improve_model_performance.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Reducing the dimensionality of images to improve model performance.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>question_6_answer_1_choices</t>
+          <t>question_8_answer_1_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>reducing_the_number_of_features_of_images_to_improve_model_accuracy.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reducing the number of features of images to improve model accuracy.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>question_6_answer_2_choices</t>
+          <t>question_8_answer_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>reducing_the_dimensionality_of_images_to_reduce_the_amount_of_data_needed_for_training.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Reducing the dimensionality of images to reduce the amount of data needed for training.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>question_6_answer_2_choices</t>
+          <t>question_8_answer_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>reducing_the_number_of_features_of_images_to_improve_model_interpretability.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reducing the number of features of images to improve model interpretability.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_8_answer_2_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>reducing_the_dimensionality_of_images_for_real-time_applications.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Reducing the dimensionality of images for real-time applications.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_8_answer_2_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>reducing_the_dimensionality_of_images_to_improve_model_performance.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Reducing the dimensionality of images to improve model performance.</t>
         </is>
       </c>
     </row>
